--- a/doc/FPGA_MSXtR_TangPrimer25K_pin.xlsx
+++ b/doc/FPGA_MSXtR_TangPrimer25K_pin.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\HRA_product\FPGA_MSXtR\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D108FBFF-7285-4D6E-9C15-80EE76A40A1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B83A606C-DB42-478A-B13A-6FA766E1C1C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1111" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1112" uniqueCount="329">
   <si>
     <t>#</t>
     <phoneticPr fontId="1"/>
@@ -1240,10 +1240,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>DIO7</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>IO_SEL0</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1336,6 +1332,33 @@
       <t>コテイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DIO0</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DIO1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DIO2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DIO7</t>
+  </si>
+  <si>
+    <t>DIO3</t>
+  </si>
+  <si>
+    <t>DIO4</t>
+  </si>
+  <si>
+    <t>DIO5</t>
+  </si>
+  <si>
+    <t>DIO6</t>
   </si>
 </sst>
 </file>
@@ -1652,7 +1675,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1785,6 +1808,36 @@
     <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1797,50 +1850,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3123,7 +3137,7 @@
       <c r="AB9" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC9" s="44" t="s">
+      <c r="AC9" s="54" t="s">
         <v>245</v>
       </c>
     </row>
@@ -3184,7 +3198,7 @@
       <c r="AB10" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC10" s="44"/>
+      <c r="AC10" s="54"/>
     </row>
     <row r="11" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B11" s="11">
@@ -3247,7 +3261,7 @@
       <c r="AB11" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC11" s="44"/>
+      <c r="AC11" s="54"/>
     </row>
     <row r="12" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B12" s="11">
@@ -3308,7 +3322,7 @@
       <c r="AB12" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC12" s="44"/>
+      <c r="AC12" s="54"/>
     </row>
     <row r="13" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B13" s="8">
@@ -3373,7 +3387,7 @@
       <c r="AB13" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC13" s="44"/>
+      <c r="AC13" s="54"/>
     </row>
     <row r="14" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B14" s="28">
@@ -3442,7 +3456,7 @@
       <c r="AB14" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC14" s="44"/>
+      <c r="AC14" s="54"/>
     </row>
     <row r="15" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B15" s="28">
@@ -3705,7 +3719,7 @@
       <c r="AB18" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC18" s="45" t="s">
+      <c r="AC18" s="55" t="s">
         <v>246</v>
       </c>
     </row>
@@ -3770,7 +3784,7 @@
       <c r="AB19" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC19" s="45"/>
+      <c r="AC19" s="55"/>
     </row>
     <row r="20" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B20" s="8">
@@ -3829,7 +3843,7 @@
       <c r="AB20" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC20" s="45"/>
+      <c r="AC20" s="55"/>
     </row>
     <row r="21" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B21" s="8">
@@ -3892,7 +3906,7 @@
       <c r="AB21" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="AC21" s="45"/>
+      <c r="AC21" s="55"/>
     </row>
     <row r="22" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B22" s="21">
@@ -3953,7 +3967,7 @@
       <c r="AB22" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC22" s="44" t="s">
+      <c r="AC22" s="54" t="s">
         <v>244</v>
       </c>
     </row>
@@ -4016,7 +4030,7 @@
       <c r="AB23" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC23" s="44"/>
+      <c r="AC23" s="54"/>
     </row>
     <row r="24" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B24" s="8">
@@ -4077,7 +4091,7 @@
       <c r="AB24" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC24" s="44"/>
+      <c r="AC24" s="54"/>
     </row>
     <row r="25" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B25" s="21">
@@ -4136,7 +4150,7 @@
       <c r="AB25" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC25" s="44"/>
+      <c r="AC25" s="54"/>
     </row>
     <row r="26" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B26" s="21">
@@ -4199,7 +4213,7 @@
       <c r="AB26" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC26" s="44"/>
+      <c r="AC26" s="54"/>
     </row>
     <row r="27" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B27" s="8">
@@ -4260,7 +4274,7 @@
       <c r="AB27" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC27" s="44"/>
+      <c r="AC27" s="54"/>
     </row>
     <row r="28" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B28" s="21">
@@ -5144,7 +5158,7 @@
       <c r="AB9" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC9" s="44" t="s">
+      <c r="AC9" s="54" t="s">
         <v>245</v>
       </c>
     </row>
@@ -5213,7 +5227,7 @@
       <c r="AB10" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC10" s="44"/>
+      <c r="AC10" s="54"/>
     </row>
     <row r="11" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B11" s="11">
@@ -5280,7 +5294,7 @@
       <c r="AB11" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC11" s="44"/>
+      <c r="AC11" s="54"/>
     </row>
     <row r="12" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B12" s="11">
@@ -5347,7 +5361,7 @@
       <c r="AB12" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC12" s="44"/>
+      <c r="AC12" s="54"/>
     </row>
     <row r="13" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B13" s="8">
@@ -5416,7 +5430,7 @@
       <c r="AB13" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC13" s="44"/>
+      <c r="AC13" s="54"/>
     </row>
     <row r="14" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B14" s="28">
@@ -5489,7 +5503,7 @@
       <c r="AB14" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC14" s="44"/>
+      <c r="AC14" s="54"/>
     </row>
     <row r="15" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B15" s="28">
@@ -5774,7 +5788,7 @@
       <c r="AB18" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC18" s="45" t="s">
+      <c r="AC18" s="55" t="s">
         <v>246</v>
       </c>
     </row>
@@ -5843,7 +5857,7 @@
       <c r="AB19" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC19" s="45"/>
+      <c r="AC19" s="55"/>
     </row>
     <row r="20" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B20" s="8">
@@ -5910,7 +5924,7 @@
       <c r="AB20" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC20" s="45"/>
+      <c r="AC20" s="55"/>
     </row>
     <row r="21" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B21" s="8">
@@ -5981,7 +5995,7 @@
       <c r="AB21" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="AC21" s="45"/>
+      <c r="AC21" s="55"/>
     </row>
     <row r="22" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B22" s="21">
@@ -6046,7 +6060,7 @@
       <c r="AB22" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC22" s="44" t="s">
+      <c r="AC22" s="54" t="s">
         <v>244</v>
       </c>
     </row>
@@ -6113,7 +6127,7 @@
       <c r="AB23" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC23" s="44"/>
+      <c r="AC23" s="54"/>
     </row>
     <row r="24" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B24" s="8">
@@ -6178,7 +6192,7 @@
       <c r="AB24" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AC24" s="44"/>
+      <c r="AC24" s="54"/>
     </row>
     <row r="25" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B25" s="21">
@@ -6241,7 +6255,7 @@
       <c r="AB25" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC25" s="44"/>
+      <c r="AC25" s="54"/>
     </row>
     <row r="26" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B26" s="21">
@@ -6304,7 +6318,7 @@
       <c r="AB26" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC26" s="44"/>
+      <c r="AC26" s="54"/>
     </row>
     <row r="27" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B27" s="8">
@@ -6369,7 +6383,7 @@
       <c r="AB27" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="AC27" s="44"/>
+      <c r="AC27" s="54"/>
     </row>
     <row r="28" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B28" s="21">
@@ -6498,7 +6512,7 @@
       <c r="AB29" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="AC29" s="46" t="s">
+      <c r="AC29" s="56" t="s">
         <v>243</v>
       </c>
     </row>
@@ -6569,7 +6583,7 @@
       <c r="AB30" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="AC30" s="46"/>
+      <c r="AC30" s="56"/>
     </row>
     <row r="31" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B31" s="21">
@@ -6634,7 +6648,7 @@
       <c r="AB31" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="AC31" s="46"/>
+      <c r="AC31" s="56"/>
     </row>
     <row r="32" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B32" s="21">
@@ -6697,7 +6711,7 @@
       <c r="AB32" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="AC32" s="46"/>
+      <c r="AC32" s="56"/>
     </row>
     <row r="33" spans="2:28" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B33" s="13">
@@ -6801,14 +6815,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:16" x14ac:dyDescent="0.15">
-      <c r="B1" s="47" t="s">
+      <c r="B1" s="57" t="s">
         <v>248</v>
       </c>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
       <c r="H1" s="34"/>
     </row>
     <row r="2" spans="2:16" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
@@ -6867,7 +6881,7 @@
       <c r="G4" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H4" s="48"/>
+      <c r="H4" s="33"/>
       <c r="J4" s="8">
         <v>40</v>
       </c>
@@ -6904,7 +6918,7 @@
       <c r="G5" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H5" s="59"/>
+      <c r="H5" s="52"/>
       <c r="J5" s="8">
         <v>39</v>
       </c>
@@ -6941,7 +6955,7 @@
       <c r="G6" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H6" s="59"/>
+      <c r="H6" s="52"/>
       <c r="J6" s="11">
         <v>38</v>
       </c>
@@ -6953,13 +6967,13 @@
       </c>
       <c r="M6" s="35"/>
       <c r="N6" s="24" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="O6" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P6" s="58" t="s">
-        <v>319</v>
+      <c r="P6" s="51" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.15">
@@ -6979,7 +6993,7 @@
       <c r="G7" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H7" s="59"/>
+      <c r="H7" s="52"/>
       <c r="J7" s="11">
         <v>37</v>
       </c>
@@ -6998,7 +7012,7 @@
       <c r="O7" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="P7" s="57"/>
+      <c r="P7" s="50"/>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B8" s="11">
@@ -7011,11 +7025,11 @@
         <v>1</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="F8" s="62"/>
+        <v>319</v>
+      </c>
+      <c r="F8" s="53"/>
       <c r="G8" s="12"/>
-      <c r="H8" s="59"/>
+      <c r="H8" s="52"/>
       <c r="J8" s="11">
         <v>36</v>
       </c>
@@ -7026,11 +7040,11 @@
         <v>4</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="N8" s="62"/>
-      <c r="O8" s="60"/>
-      <c r="P8" s="53"/>
+        <v>319</v>
+      </c>
+      <c r="N8" s="53"/>
+      <c r="O8" s="12"/>
+      <c r="P8" s="47"/>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B9" s="11">
@@ -7051,7 +7065,7 @@
       <c r="G9" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H9" s="59"/>
+      <c r="H9" s="52"/>
       <c r="J9" s="11">
         <v>35</v>
       </c>
@@ -7062,11 +7076,11 @@
         <v>4</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="N9" s="62"/>
+        <v>319</v>
+      </c>
+      <c r="N9" s="53"/>
       <c r="O9" s="12"/>
-      <c r="P9" s="59"/>
+      <c r="P9" s="52"/>
     </row>
     <row r="10" spans="2:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="11">
@@ -7087,7 +7101,7 @@
       <c r="G10" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H10" s="59"/>
+      <c r="H10" s="52"/>
       <c r="J10" s="11">
         <v>34</v>
       </c>
@@ -7106,8 +7120,8 @@
       <c r="O10" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P10" s="46" t="s">
-        <v>307</v>
+      <c r="P10" s="56" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="11" spans="2:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -7121,11 +7135,11 @@
         <v>5</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="F11" s="62"/>
+        <v>319</v>
+      </c>
+      <c r="F11" s="53"/>
       <c r="G11" s="12"/>
-      <c r="H11" s="59"/>
+      <c r="H11" s="52"/>
       <c r="J11" s="11">
         <v>33</v>
       </c>
@@ -7144,7 +7158,7 @@
       <c r="O11" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P11" s="46"/>
+      <c r="P11" s="56"/>
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B12" s="11">
@@ -7157,11 +7171,11 @@
         <v>5</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="F12" s="62"/>
+        <v>319</v>
+      </c>
+      <c r="F12" s="53"/>
       <c r="G12" s="12"/>
-      <c r="H12" s="48"/>
+      <c r="H12" s="33"/>
       <c r="J12" s="11">
         <v>32</v>
       </c>
@@ -7174,13 +7188,13 @@
       <c r="M12" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="N12" s="52" t="s">
-        <v>321</v>
+      <c r="N12" s="46" t="s">
+        <v>320</v>
       </c>
       <c r="O12" s="12" t="s">
-        <v>314</v>
-      </c>
-      <c r="P12" s="48"/>
+        <v>313</v>
+      </c>
+      <c r="P12" s="33"/>
     </row>
     <row r="13" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B13" s="11">
@@ -7193,11 +7207,11 @@
         <v>5</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="F13" s="62"/>
+        <v>319</v>
+      </c>
+      <c r="F13" s="53"/>
       <c r="G13" s="12"/>
-      <c r="H13" s="48"/>
+      <c r="H13" s="33"/>
       <c r="J13" s="11">
         <v>31</v>
       </c>
@@ -7208,11 +7222,11 @@
         <v>3</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="N13" s="62"/>
+        <v>319</v>
+      </c>
+      <c r="N13" s="53"/>
       <c r="O13" s="12"/>
-      <c r="P13" s="48"/>
+      <c r="P13" s="33"/>
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B14" s="11">
@@ -7225,11 +7239,11 @@
         <v>5</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="F14" s="62"/>
+        <v>319</v>
+      </c>
+      <c r="F14" s="53"/>
       <c r="G14" s="12"/>
-      <c r="H14" s="48"/>
+      <c r="H14" s="33"/>
       <c r="J14" s="11">
         <v>30</v>
       </c>
@@ -7249,7 +7263,7 @@
         <v>48</v>
       </c>
       <c r="P14" s="31" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.15">
@@ -7263,11 +7277,11 @@
         <v>5</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="F15" s="62"/>
+        <v>319</v>
+      </c>
+      <c r="F15" s="53"/>
       <c r="G15" s="12"/>
-      <c r="H15" s="48"/>
+      <c r="H15" s="33"/>
       <c r="J15" s="11">
         <v>29</v>
       </c>
@@ -7278,11 +7292,11 @@
         <v>3</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="N15" s="62"/>
-      <c r="O15" s="60"/>
-      <c r="P15" s="59"/>
+        <v>319</v>
+      </c>
+      <c r="N15" s="53"/>
+      <c r="O15" s="12"/>
+      <c r="P15" s="52"/>
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B16" s="11">
@@ -7295,11 +7309,11 @@
         <v>5</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="F16" s="62"/>
+        <v>319</v>
+      </c>
+      <c r="F16" s="53"/>
       <c r="G16" s="12"/>
-      <c r="H16" s="48"/>
+      <c r="H16" s="33"/>
       <c r="J16" s="11">
         <v>28</v>
       </c>
@@ -7310,9 +7324,9 @@
         <v>0</v>
       </c>
       <c r="M16" s="1"/>
-      <c r="N16" s="49"/>
-      <c r="O16" s="60"/>
-      <c r="P16" s="59"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="12"/>
+      <c r="P16" s="52"/>
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B17" s="11">
@@ -7325,11 +7339,11 @@
         <v>5</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="F17" s="62"/>
+        <v>319</v>
+      </c>
+      <c r="F17" s="53"/>
       <c r="G17" s="12"/>
-      <c r="H17" s="48"/>
+      <c r="H17" s="33"/>
       <c r="J17" s="11">
         <v>27</v>
       </c>
@@ -7346,7 +7360,7 @@
         <v>282</v>
       </c>
       <c r="O17" s="12"/>
-      <c r="P17" s="57"/>
+      <c r="P17" s="50"/>
     </row>
     <row r="18" spans="2:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="11">
@@ -7367,7 +7381,7 @@
       <c r="G18" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H18" s="45" t="s">
+      <c r="H18" s="55" t="s">
         <v>293</v>
       </c>
       <c r="J18" s="8">
@@ -7408,7 +7422,7 @@
       <c r="G19" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H19" s="45"/>
+      <c r="H19" s="55"/>
       <c r="J19" s="8">
         <v>25</v>
       </c>
@@ -7447,7 +7461,7 @@
       <c r="G20" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H20" s="45"/>
+      <c r="H20" s="55"/>
       <c r="J20" s="11">
         <v>24</v>
       </c>
@@ -7458,9 +7472,9 @@
         <v>1</v>
       </c>
       <c r="M20" s="1"/>
-      <c r="N20" s="49"/>
-      <c r="O20" s="60"/>
-      <c r="P20" s="59"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="12"/>
+      <c r="P20" s="52"/>
     </row>
     <row r="21" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B21" s="11">
@@ -7481,7 +7495,7 @@
       <c r="G21" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="H21" s="45"/>
+      <c r="H21" s="55"/>
       <c r="J21" s="11">
         <v>23</v>
       </c>
@@ -7492,9 +7506,9 @@
         <v>1</v>
       </c>
       <c r="M21" s="1"/>
-      <c r="N21" s="49"/>
-      <c r="O21" s="60"/>
-      <c r="P21" s="59"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="12"/>
+      <c r="P21" s="52"/>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B22" s="8">
@@ -7608,14 +7622,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:16" x14ac:dyDescent="0.15">
-      <c r="B1" s="47" t="s">
+      <c r="B1" s="57" t="s">
         <v>248</v>
       </c>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
       <c r="H1" s="34"/>
     </row>
     <row r="2" spans="2:16" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
@@ -7674,7 +7688,7 @@
       <c r="G4" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H4" s="44" t="s">
+      <c r="H4" s="54" t="s">
         <v>244</v>
       </c>
       <c r="J4" s="8">
@@ -7713,7 +7727,7 @@
       <c r="G5" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H5" s="44"/>
+      <c r="H5" s="54"/>
       <c r="J5" s="8">
         <v>39</v>
       </c>
@@ -7750,7 +7764,7 @@
       <c r="G6" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H6" s="44"/>
+      <c r="H6" s="54"/>
       <c r="J6" s="11">
         <v>38</v>
       </c>
@@ -7762,13 +7776,13 @@
       </c>
       <c r="M6" s="35"/>
       <c r="N6" s="24" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="O6" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P6" s="58" t="s">
-        <v>319</v>
+      <c r="P6" s="51" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.15">
@@ -7788,7 +7802,7 @@
       <c r="G7" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H7" s="44"/>
+      <c r="H7" s="54"/>
       <c r="J7" s="11">
         <v>37</v>
       </c>
@@ -7807,7 +7821,7 @@
       <c r="O7" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="P7" s="57"/>
+      <c r="P7" s="50"/>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B8" s="11">
@@ -7820,12 +7834,14 @@
         <v>1</v>
       </c>
       <c r="E8" s="1"/>
-      <c r="F8" s="50" t="s">
-        <v>300</v>
-      </c>
-      <c r="G8" s="12"/>
-      <c r="H8" s="54" t="s">
-        <v>316</v>
+      <c r="F8" s="44" t="s">
+        <v>321</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="H8" s="48" t="s">
+        <v>315</v>
       </c>
       <c r="J8" s="11">
         <v>36</v>
@@ -7859,7 +7875,7 @@
       <c r="G9" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H9" s="44" t="s">
+      <c r="H9" s="54" t="s">
         <v>244</v>
       </c>
       <c r="J9" s="11">
@@ -7872,14 +7888,14 @@
         <v>4</v>
       </c>
       <c r="M9" s="1"/>
-      <c r="N9" s="50" t="s">
-        <v>301</v>
+      <c r="N9" s="44" t="s">
+        <v>300</v>
       </c>
       <c r="O9" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P9" s="61" t="s">
-        <v>318</v>
+      <c r="P9" s="49" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="10" spans="2:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -7901,7 +7917,7 @@
       <c r="G10" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H10" s="44"/>
+      <c r="H10" s="54"/>
       <c r="J10" s="11">
         <v>34</v>
       </c>
@@ -7920,8 +7936,8 @@
       <c r="O10" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P10" s="46" t="s">
-        <v>307</v>
+      <c r="P10" s="56" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="11" spans="2:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -7935,14 +7951,14 @@
         <v>5</v>
       </c>
       <c r="E11" s="1"/>
-      <c r="F11" s="50" t="s">
-        <v>300</v>
+      <c r="F11" s="44" t="s">
+        <v>322</v>
       </c>
       <c r="G11" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H11" s="56" t="s">
-        <v>317</v>
+      <c r="H11" s="59" t="s">
+        <v>316</v>
       </c>
       <c r="J11" s="11">
         <v>33</v>
@@ -7962,7 +7978,7 @@
       <c r="O11" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="P11" s="46"/>
+      <c r="P11" s="56"/>
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B12" s="11">
@@ -7975,13 +7991,13 @@
         <v>5</v>
       </c>
       <c r="E12" s="1"/>
-      <c r="F12" s="50" t="s">
-        <v>300</v>
+      <c r="F12" s="44" t="s">
+        <v>323</v>
       </c>
       <c r="G12" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H12" s="56"/>
+      <c r="H12" s="59"/>
       <c r="J12" s="11">
         <v>32</v>
       </c>
@@ -7994,13 +8010,13 @@
       <c r="M12" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="N12" s="52" t="s">
+      <c r="N12" s="46" t="s">
+        <v>312</v>
+      </c>
+      <c r="O12" s="12" t="s">
         <v>313</v>
       </c>
-      <c r="O12" s="12" t="s">
-        <v>314</v>
-      </c>
-      <c r="P12" s="48"/>
+      <c r="P12" s="33"/>
     </row>
     <row r="13" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B13" s="11">
@@ -8013,13 +8029,13 @@
         <v>5</v>
       </c>
       <c r="E13" s="1"/>
-      <c r="F13" s="50" t="s">
-        <v>300</v>
+      <c r="F13" s="44" t="s">
+        <v>325</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="H13" s="56"/>
+        <v>210</v>
+      </c>
+      <c r="H13" s="59"/>
       <c r="J13" s="11">
         <v>31</v>
       </c>
@@ -8031,13 +8047,13 @@
       </c>
       <c r="M13" s="1"/>
       <c r="N13" s="18" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="O13" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P13" s="46" t="s">
-        <v>307</v>
+      <c r="P13" s="56" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.15">
@@ -8051,13 +8067,13 @@
         <v>5</v>
       </c>
       <c r="E14" s="1"/>
-      <c r="F14" s="50" t="s">
-        <v>300</v>
+      <c r="F14" s="44" t="s">
+        <v>326</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="H14" s="56"/>
+        <v>210</v>
+      </c>
+      <c r="H14" s="59"/>
       <c r="J14" s="11">
         <v>30</v>
       </c>
@@ -8076,7 +8092,7 @@
       <c r="O14" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="P14" s="46"/>
+      <c r="P14" s="56"/>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B15" s="11">
@@ -8089,13 +8105,13 @@
         <v>5</v>
       </c>
       <c r="E15" s="1"/>
-      <c r="F15" s="50" t="s">
-        <v>300</v>
+      <c r="F15" s="44" t="s">
+        <v>327</v>
       </c>
       <c r="G15" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H15" s="56"/>
+      <c r="H15" s="59"/>
       <c r="J15" s="11">
         <v>29</v>
       </c>
@@ -8106,14 +8122,14 @@
         <v>3</v>
       </c>
       <c r="M15" s="1"/>
-      <c r="N15" s="50" t="s">
-        <v>302</v>
+      <c r="N15" s="44" t="s">
+        <v>301</v>
       </c>
       <c r="O15" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P15" s="56" t="s">
-        <v>318</v>
+      <c r="P15" s="59" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.15">
@@ -8127,13 +8143,13 @@
         <v>5</v>
       </c>
       <c r="E16" s="1"/>
-      <c r="F16" s="50" t="s">
-        <v>300</v>
+      <c r="F16" s="44" t="s">
+        <v>328</v>
       </c>
       <c r="G16" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H16" s="56"/>
+      <c r="H16" s="59"/>
       <c r="J16" s="11">
         <v>28</v>
       </c>
@@ -8144,13 +8160,13 @@
         <v>0</v>
       </c>
       <c r="M16" s="1"/>
-      <c r="N16" s="50" t="s">
-        <v>303</v>
+      <c r="N16" s="44" t="s">
+        <v>302</v>
       </c>
       <c r="O16" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P16" s="56"/>
+      <c r="P16" s="59"/>
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B17" s="11">
@@ -8163,13 +8179,13 @@
         <v>5</v>
       </c>
       <c r="E17" s="1"/>
-      <c r="F17" s="50" t="s">
-        <v>300</v>
+      <c r="F17" s="44" t="s">
+        <v>324</v>
       </c>
       <c r="G17" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="H17" s="56"/>
+      <c r="H17" s="59"/>
       <c r="J17" s="11">
         <v>27</v>
       </c>
@@ -8186,7 +8202,7 @@
         <v>282</v>
       </c>
       <c r="O17" s="12"/>
-      <c r="P17" s="57"/>
+      <c r="P17" s="50"/>
     </row>
     <row r="18" spans="2:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="11">
@@ -8207,7 +8223,7 @@
       <c r="G18" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H18" s="45" t="s">
+      <c r="H18" s="55" t="s">
         <v>293</v>
       </c>
       <c r="J18" s="8">
@@ -8248,7 +8264,7 @@
       <c r="G19" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H19" s="45"/>
+      <c r="H19" s="55"/>
       <c r="J19" s="8">
         <v>25</v>
       </c>
@@ -8287,7 +8303,7 @@
       <c r="G20" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H20" s="45"/>
+      <c r="H20" s="55"/>
       <c r="J20" s="11">
         <v>24</v>
       </c>
@@ -8298,14 +8314,14 @@
         <v>1</v>
       </c>
       <c r="M20" s="1"/>
-      <c r="N20" s="51" t="s">
-        <v>304</v>
+      <c r="N20" s="45" t="s">
+        <v>303</v>
       </c>
       <c r="O20" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P20" s="55" t="s">
-        <v>318</v>
+      <c r="P20" s="58" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="21" spans="2:16" x14ac:dyDescent="0.15">
@@ -8327,7 +8343,7 @@
       <c r="G21" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="H21" s="45"/>
+      <c r="H21" s="55"/>
       <c r="J21" s="11">
         <v>23</v>
       </c>
@@ -8338,13 +8354,13 @@
         <v>1</v>
       </c>
       <c r="M21" s="1"/>
-      <c r="N21" s="51" t="s">
-        <v>305</v>
+      <c r="N21" s="45" t="s">
+        <v>304</v>
       </c>
       <c r="O21" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="P21" s="55"/>
+      <c r="P21" s="58"/>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B22" s="8">
@@ -8424,34 +8440,36 @@
     </row>
     <row r="36" spans="13:14" x14ac:dyDescent="0.15">
       <c r="M36" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N36" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="37" spans="13:14" x14ac:dyDescent="0.15">
       <c r="M37" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="38" spans="13:14" x14ac:dyDescent="0.15">
       <c r="M38" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="39" spans="13:14" x14ac:dyDescent="0.15">
       <c r="M39" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="40" spans="13:14" x14ac:dyDescent="0.15">
       <c r="M40" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="H18:H21"/>
     <mergeCell ref="P20:P21"/>
     <mergeCell ref="P15:P16"/>
     <mergeCell ref="P13:P14"/>
@@ -8459,8 +8477,6 @@
     <mergeCell ref="H4:H7"/>
     <mergeCell ref="H11:H17"/>
     <mergeCell ref="H9:H10"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="H18:H21"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
